--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2C1793-C03E-A143-86C0-6AB006BD8C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB2F11C-4DBE-734E-BD13-B3DAE90A935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2180" yWindow="5400" windowWidth="28000" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="0" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -183,6 +183,114 @@
   </si>
   <si>
     <t>Frame</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-09.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-10.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-11.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.100.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>室內設計</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-12.jpeg</t>
+  </si>
+  <si>
+    <t>HomeStyler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>線上／手機室內設計軟件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.homestyler.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IKEA Home Planner</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IKEA產品專用線上室內設計軟件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ikea.com.hk/en/ikea-planner</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armstrong Flooring Design a Room</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>線上地板／油漆虛擬軟體</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.armstrongflooring.com/residential/en-us/inspiration/design-a-room.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>室內設計界百科全書</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>室內設計、裝潢設計社群平台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传播世界建筑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界上最具影响力的建筑、室内设计和设计杂志</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>架构和设计平台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荷蘭雜誌《Frame》成立於1997年，是世界領先的室內設計專業媒體品牌。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯聚全台灣的設計公司、裝修設計作品、裝修知識和經驗的裝修平台。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -190,7 +298,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -220,6 +328,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -578,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -650,13 +765,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="17">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
@@ -667,13 +785,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="17">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
@@ -684,13 +805,16 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
@@ -701,13 +825,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="34">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="D7" s="2" t="s">
         <v>30</v>
       </c>
@@ -718,13 +845,16 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="C8" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="D8" s="2" t="s">
         <v>31</v>
       </c>
@@ -735,13 +865,16 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="34">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
@@ -750,6 +883,86 @@
       </c>
       <c r="F9" s="4" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="34">
+      <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17">
+      <c r="A12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -762,6 +975,10 @@
     <hyperlink ref="F7" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
     <hyperlink ref="F8" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
     <hyperlink ref="F9" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB2F11C-4DBE-734E-BD13-B3DAE90A935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AE9693-EBC5-BB45-BB5E-9BA201DF25E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -291,6 +291,103 @@
   </si>
   <si>
     <t>匯聚全台灣的設計公司、裝修設計作品、裝修知識和經驗的裝修平台。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>013</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-13.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/watch/xielaoshi123/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢老师说装修</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Facebook </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>公開社團</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.chaoling-id.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-14.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>014</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChaoLing Interior Design</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>室內裝潢樣品展</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>015</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://medium.com/@sandynespace/%E7%A4%BE%E5%9C%98-%E8%A8%8E%E8%AB%96%E5%8D%80-ca1690640b6d</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臉書 室內設計討論區匯總</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臉書相關 社團匯總</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-15.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.fe.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>016</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-16.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>富億空間設計</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -693,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -767,202 +864,282 @@
     </row>
     <row r="4" spans="1:6" ht="17">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
+      <c r="F4" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="34">
+      <c r="F6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34">
       <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="34">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="34">
-      <c r="A10" s="1" t="s">
+    <row r="12" spans="1:6" ht="34">
+      <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17">
-      <c r="A11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17">
-      <c r="A12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17">
       <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17">
+      <c r="A15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17">
+      <c r="A16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="17">
+      <c r="A17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -970,15 +1147,19 @@
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F7" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F8" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F9" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F10" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F11" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F12" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F13" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F11" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F12" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F13" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F14" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F15" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F4" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
+    <hyperlink ref="F16" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F5" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F17" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AE9693-EBC5-BB45-BB5E-9BA201DF25E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543EB4EE-03C3-DB47-B49B-727C58C96B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="1040" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="90">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -388,6 +388,22 @@
   </si>
   <si>
     <t>富億空間設計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>017</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/watch/zhuangxiuxinshijie2/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝修新飾界2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-17.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -790,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -884,261 +900,281 @@
     </row>
     <row r="5" spans="1:6" ht="17">
       <c r="A5" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>24</v>
+      <c r="F6" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>27</v>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="34">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:6" ht="34">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="17">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:6" ht="17">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="34">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="34">
       <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="34">
+      <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="17">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17">
       <c r="A17" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="17">
+      <c r="A18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1147,19 +1183,20 @@
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F7" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F8" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F9" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F10" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F11" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F12" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F13" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F14" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F15" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F15" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F16" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
     <hyperlink ref="F4" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
-    <hyperlink ref="F16" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
-    <hyperlink ref="F5" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
-    <hyperlink ref="F17" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F17" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F6" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F18" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F5" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543EB4EE-03C3-DB47-B49B-727C58C96B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EB83F3-EF43-C046-9256-BDFE7E6D46E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="20" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="94">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -404,6 +404,22 @@
   </si>
   <si>
     <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-17.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>018</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝修設計分享網</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ZHUANGXIUFENXIANG/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-18.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -806,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -920,261 +936,281 @@
     </row>
     <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>24</v>
+      <c r="F7" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>27</v>
+      <c r="F8" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17">
       <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="34">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:6" ht="34">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:6" ht="17">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="34">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="34">
       <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="34">
+      <c r="A14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="17">
-      <c r="A14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17">
       <c r="A18" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="17">
+      <c r="A19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="E19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1183,20 +1219,21 @@
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F8" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F11" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F12" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F13" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F14" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F15" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F10" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F11" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F17" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
     <hyperlink ref="F4" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
-    <hyperlink ref="F17" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
-    <hyperlink ref="F6" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
-    <hyperlink ref="F18" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F18" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F7" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F19" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
     <hyperlink ref="F5" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
+    <hyperlink ref="F6" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EB83F3-EF43-C046-9256-BDFE7E6D46E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1928B603-A457-9947-AC25-BA233C979941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -420,6 +420,22 @@
   </si>
   <si>
     <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-18.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>019</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-19.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實用裝修Nice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/syzxnice/?ti=as</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -822,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -956,261 +972,281 @@
     </row>
     <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
+      <c r="F8" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>27</v>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17">
       <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="34">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:6" ht="34">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:6" ht="17">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="34">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="34">
       <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="34">
+      <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="17">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17">
       <c r="A19" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17">
+      <c r="A20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="E20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1219,21 +1255,22 @@
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F9" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F10" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F11" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F13" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F14" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F16" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F17" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F10" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F11" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F12" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F13" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F14" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F15" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F16" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F17" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F18" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
     <hyperlink ref="F4" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
-    <hyperlink ref="F18" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
-    <hyperlink ref="F7" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
-    <hyperlink ref="F19" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F19" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F8" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F20" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
     <hyperlink ref="F5" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
     <hyperlink ref="F6" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
+    <hyperlink ref="F7" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1928B603-A457-9947-AC25-BA233C979941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FB0BC4-3E60-9148-BE04-6E2BD139187C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="0" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -436,6 +436,26 @@
   </si>
   <si>
     <t>https://www.facebook.com/syzxnice/?ti=as</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoME Panasonic 體驗館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panasonic 在生活中的每一個場景，都能為您帶來理想的美好提案</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pstw.panasonic.com.tw/PoME/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-20.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -838,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -870,407 +890,428 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17">
+    <row r="2" spans="1:6" ht="34">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>24</v>
+      <c r="F9" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>27</v>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17">
       <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="34">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:6" ht="34">
+      <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:6" ht="17">
+      <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="34">
-      <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="34">
       <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="34">
+      <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17">
-      <c r="A16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17">
       <c r="A19" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17">
       <c r="A20" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17">
+      <c r="A21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="4" t="s">
+      <c r="E21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F10" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F11" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F12" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F13" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F14" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F15" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F16" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F17" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F18" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
-    <hyperlink ref="F4" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
-    <hyperlink ref="F19" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
-    <hyperlink ref="F8" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
-    <hyperlink ref="F20" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
-    <hyperlink ref="F5" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
-    <hyperlink ref="F6" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
-    <hyperlink ref="F7" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
+    <hyperlink ref="F11" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F12" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F13" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F14" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F15" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F16" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F17" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F18" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F19" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F5" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
+    <hyperlink ref="F20" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F9" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F21" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F6" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
+    <hyperlink ref="F7" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
+    <hyperlink ref="F8" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
+    <hyperlink ref="F2" r:id="rId19" xr:uid="{2D8AA33C-D653-6F4E-8CD3-2B3193ED6FCE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FB0BC4-3E60-9148-BE04-6E2BD139187C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E62C0E-FD90-8D4F-A5F8-F7A56BB686A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -456,6 +456,26 @@
   </si>
   <si>
     <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-20.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>021</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lo-Fi House</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空間風格規劃師</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LofihouseStylist/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-21.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -858,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -890,428 +910,449 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="34">
+    <row r="2" spans="1:6" ht="17">
       <c r="A2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34">
+      <c r="A3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="17">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17">
       <c r="A9" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>24</v>
+      <c r="F10" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>27</v>
+      <c r="F11" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17">
       <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="34">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:6" ht="34">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="17">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:6" ht="17">
+      <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="34">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="34">
       <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="34">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="17">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17">
       <c r="A21" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
-    <hyperlink ref="F4" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F11" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F12" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F13" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F14" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F15" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F16" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F17" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F18" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F19" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
-    <hyperlink ref="F5" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
-    <hyperlink ref="F20" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
-    <hyperlink ref="F9" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
-    <hyperlink ref="F21" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
-    <hyperlink ref="F6" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
-    <hyperlink ref="F7" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
-    <hyperlink ref="F8" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
-    <hyperlink ref="F2" r:id="rId19" xr:uid="{2D8AA33C-D653-6F4E-8CD3-2B3193ED6FCE}"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
+    <hyperlink ref="F12" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F13" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F14" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F15" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F16" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F17" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F18" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F19" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F20" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F6" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
+    <hyperlink ref="F21" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F10" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F22" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F7" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
+    <hyperlink ref="F8" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
+    <hyperlink ref="F9" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
+    <hyperlink ref="F3" r:id="rId19" xr:uid="{2D8AA33C-D653-6F4E-8CD3-2B3193ED6FCE}"/>
+    <hyperlink ref="F2" r:id="rId20" xr:uid="{C77323EC-0EE9-C847-87E5-0C7811FAB4CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-4603-InteriorDesign.xlsx
+++ b/db/A7XLK-4603-InteriorDesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E62C0E-FD90-8D4F-A5F8-F7A56BB686A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF205706-0082-5648-AD8F-4D26183D9EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="940" windowWidth="27980" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="0" yWindow="940" windowWidth="27800" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="112">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -476,6 +476,21 @@
   </si>
   <si>
     <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-21.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>022</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝潢大公開</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/watch/446776782574726/1219914835439506/</t>
+  </si>
+  <si>
+    <t>fig/XLK-461-AirPulifier/XLK-4603-InteriorDesign-22.jpeg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -878,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -912,447 +927,467 @@
     </row>
     <row r="2" spans="1:6" ht="17">
       <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17">
+      <c r="A3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="34">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:6" ht="34">
+      <c r="A4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="17">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17">
       <c r="A8" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17">
       <c r="A9" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>24</v>
+      <c r="F11" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>27</v>
+      <c r="F12" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17">
       <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="34">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:6" ht="34">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:6" ht="17">
+      <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="34">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="34">
       <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="34">
+      <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="17">
-      <c r="A18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="17">
       <c r="A22" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="17">
+      <c r="A23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="E23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
-    <hyperlink ref="F12" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
-    <hyperlink ref="F13" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
-    <hyperlink ref="F14" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
-    <hyperlink ref="F15" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
-    <hyperlink ref="F16" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
-    <hyperlink ref="F17" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
-    <hyperlink ref="F18" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
-    <hyperlink ref="F19" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
-    <hyperlink ref="F20" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
-    <hyperlink ref="F6" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
-    <hyperlink ref="F21" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
-    <hyperlink ref="F10" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
-    <hyperlink ref="F22" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
-    <hyperlink ref="F7" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
-    <hyperlink ref="F8" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
-    <hyperlink ref="F9" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
-    <hyperlink ref="F3" r:id="rId19" xr:uid="{2D8AA33C-D653-6F4E-8CD3-2B3193ED6FCE}"/>
-    <hyperlink ref="F2" r:id="rId20" xr:uid="{C77323EC-0EE9-C847-87E5-0C7811FAB4CA}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{FB460E26-B45D-7043-AD4A-5925A22003A1}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{4FED19D3-BAE1-B547-857C-B29BF0874898}"/>
+    <hyperlink ref="F13" r:id="rId3" xr:uid="{7A98975D-EB4C-074B-9464-DCBC47EAAE0F}"/>
+    <hyperlink ref="F14" r:id="rId4" xr:uid="{44F3E530-B525-0A45-8E13-EA6F931838B4}"/>
+    <hyperlink ref="F15" r:id="rId5" xr:uid="{B4B02033-CF26-5D48-8B8A-375B94A5BB6A}"/>
+    <hyperlink ref="F16" r:id="rId6" xr:uid="{AA4D0EF0-AC9B-0F4C-B090-CA1694A095D5}"/>
+    <hyperlink ref="F17" r:id="rId7" xr:uid="{05A3CFF3-6D4E-3F44-AB63-F84843E926B4}"/>
+    <hyperlink ref="F18" r:id="rId8" xr:uid="{E917D357-4624-B744-A958-4743C4469581}"/>
+    <hyperlink ref="F19" r:id="rId9" xr:uid="{EEDF6C64-E918-CE41-8068-FC207D2613CC}"/>
+    <hyperlink ref="F20" r:id="rId10" xr:uid="{04F8EDCD-180C-7C4F-BF87-71D1C0628947}"/>
+    <hyperlink ref="F21" r:id="rId11" xr:uid="{1ABCA4D8-DDF6-074C-AAB0-CD75B6288500}"/>
+    <hyperlink ref="F7" r:id="rId12" xr:uid="{A880E88B-4DAA-8948-9523-88AF1A5C3926}"/>
+    <hyperlink ref="F22" r:id="rId13" xr:uid="{37083AB6-E851-7D4F-88B3-20DE02B2DC40}"/>
+    <hyperlink ref="F11" r:id="rId14" xr:uid="{203A1B0B-7A12-6E4D-8B31-1AE665EB2BE5}"/>
+    <hyperlink ref="F23" r:id="rId15" xr:uid="{811536DA-5DAB-0F4C-ADF9-04446202D024}"/>
+    <hyperlink ref="F8" r:id="rId16" xr:uid="{D4A11F6F-F94B-AF42-951A-584BD2BC674E}"/>
+    <hyperlink ref="F9" r:id="rId17" xr:uid="{76908B42-E775-AE42-8205-98EF44DF51B9}"/>
+    <hyperlink ref="F10" r:id="rId18" xr:uid="{73CF4E5D-4BCE-CA43-A42E-ACB3E856EE62}"/>
+    <hyperlink ref="F4" r:id="rId19" xr:uid="{2D8AA33C-D653-6F4E-8CD3-2B3193ED6FCE}"/>
+    <hyperlink ref="F3" r:id="rId20" xr:uid="{C77323EC-0EE9-C847-87E5-0C7811FAB4CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
